--- a/藥物資料.xlsx
+++ b/藥物資料.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/catherine/Projects/icu-antibiotic-tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92998D07-DD1A-884F-BAA0-AB00FF0A02AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D4B726-4347-434F-BA10-EF68AB54B5D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="320" yWindow="580" windowWidth="24940" windowHeight="14580" xr2:uid="{B8F06AC8-2EDC-9A46-8DCC-77D015794BF5}"/>
+    <workbookView xWindow="15600" yWindow="580" windowWidth="10000" windowHeight="14520" xr2:uid="{B8F06AC8-2EDC-9A46-8DCC-77D015794BF5}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="55">
   <si>
     <t>英文商品名</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,21 +52,12 @@
     <t>Sevatrim</t>
   </si>
   <si>
-    <t>Trimethoprim 80 mg + Sulfamethoxazole 400 mg</t>
-  </si>
-  <si>
     <t>Bobimixyn</t>
   </si>
   <si>
-    <t>500 KIU/Vial</t>
-  </si>
-  <si>
     <t>Brosym</t>
   </si>
   <si>
-    <t>Cefoperazone/Sulbactam 1/1 g</t>
-  </si>
-  <si>
     <t>Seforce</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -83,23 +74,183 @@
     <t>Cresemba</t>
   </si>
   <si>
-    <t>200mg/vial</t>
-  </si>
-  <si>
     <t>Ganciclovir</t>
   </si>
   <si>
-    <t>500mg/Vial</t>
-  </si>
-  <si>
     <t>Diflucan</t>
+  </si>
+  <si>
+    <t>Eraxis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flumarin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tatumcef</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fungizone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AmBisome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ampholipad</t>
+  </si>
+  <si>
+    <t>Ertapenem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Antifect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cefmore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Meropenem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Myfungin </t>
+  </si>
+  <si>
+    <t>Cefin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tapimycin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Teicod</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Culin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tygacil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sulampi</t>
+  </si>
+  <si>
+    <t>U-Vanco</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vfend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zavicefta</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cetazone</t>
+  </si>
+  <si>
+    <t>Zerbaxa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zinforo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zovirax</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Each ampoule (5ml) contains: Trimethoprim 80 mg + Sulfamethoxazole 400 mg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>500 KIU/Vial，乾粉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cefoperazone/Sulbactam 1/1 g，乾粉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200 mg/vial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>500 mg/Vial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2 mg/mL, 50 mL/Bot</t>
+  </si>
+  <si>
+    <t>100 mg/Vial，乾粉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000 mg/Vial，乾粉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2000 mg/Vial，乾粉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50 mg/Vial</t>
+  </si>
+  <si>
+    <t>500 mg/Vial，乾粉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50 mg/Vial，乾粉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Piperacillin/Tazo 2g/250mg，乾粉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200 mg/Vial，乾粉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ampicillin/Sulbactam 1 g/0.5 g，乾粉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ceftazidime/Avibactam 2/0.5 g，乾粉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ceftolozane 1g + tazobactam 0.5g，乾粉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>600 mg/Vial，乾粉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>250 mg/Vial，乾粉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -112,6 +263,14 @@
       <sz val="9"/>
       <name val="新細明體"/>
       <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -138,8 +297,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -476,11 +638,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C251DAC-3078-1649-A220-CB0D4A43817D}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
-    <col min="2" max="2" width="56.1640625" customWidth="1"/>
+    <col min="2" max="2" width="65.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -496,60 +658,255 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
         <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
